--- a/example/reports/platform_firewall-review.xlsx
+++ b/example/reports/platform_firewall-review.xlsx
@@ -72,7 +72,7 @@
     <t>Backup timestamp</t>
   </si>
   <si>
-    <t>2026-08-26 23:14</t>
+    <t>2026-08-27 00:01</t>
   </si>
   <si>
     <t>Report generated</t>
@@ -945,7 +945,7 @@
     <t>Past its stated expiry date</t>
   </si>
   <si>
-    <t>The description gives an expiry of 2026-06-13, 74 days ago, but the rule is still active.</t>
+    <t>The description gives an expiry of 2026-06-13, 75 days ago, but the rule is still active.</t>
   </si>
   <si>
     <t>Remove the rule, or extend it with a new change reference.</t>
@@ -1050,7 +1050,7 @@
     <t>Expires soon</t>
   </si>
   <si>
-    <t>The stated expiry is 2026-08-27, in 1 days.</t>
+    <t>The stated expiry is 2026-08-27, in 0 days.</t>
   </si>
   <si>
     <t>Confirm whether the access is still needed before it lapses.</t>
